--- a/documents/backlog_atmos.xlsx
+++ b/documents/backlog_atmos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6d47aa5dd819dd88/Desktop/Atmos/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49818CB5-BCCE-41CC-8413-E1C28DA3E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{49818CB5-BCCE-41CC-8413-E1C28DA3E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54345960-ECB7-4D15-8AC3-97A6F01F004A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B778ACF6-2913-43EF-AFE6-AC9B8CA95E6D}"/>
   </bookViews>
@@ -16,9 +16,6 @@
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
     <sheet name="Lista - Validações" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
   <si>
     <t>REQUISITOS</t>
   </si>
@@ -108,9 +105,6 @@
     <t>SP3</t>
   </si>
   <si>
-    <t>SP4</t>
-  </si>
-  <si>
     <t>Conterá o contexto e justificativa da criação do projeto</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>Desenvolver prototipagente da tela de dashborad</t>
   </si>
   <si>
-    <t>Implementar responsividade no site</t>
-  </si>
-  <si>
     <t>Criar Documentação</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>Criar User Stories</t>
   </si>
   <si>
-    <t>Desenvolver de Gerenciamento de Banco de Dados</t>
-  </si>
-  <si>
     <t>Desenvolver Modelagem Lógica</t>
   </si>
   <si>
@@ -256,6 +244,21 @@
   </si>
   <si>
     <t>Entregue</t>
+  </si>
+  <si>
+    <t>Desenvolver Gerenciamento de Banco de Dados</t>
+  </si>
+  <si>
+    <t>Desenvolver Leitura dados (CPU, RAM e Disco) de máquina via Python</t>
+  </si>
+  <si>
+    <t>Implementar responsividade no site institucional</t>
+  </si>
+  <si>
+    <t>Desenvolver tela sobre</t>
+  </si>
+  <si>
+    <t>Criar tela sobre referente a empresa</t>
   </si>
 </sst>
 </file>
@@ -335,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -359,45 +362,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.79998168889431442"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="3" tint="0.749992370372631"/>
       </left>
@@ -412,69 +376,186 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -492,20 +573,991 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>PLANEJADO</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> X ENTREGUE</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lista - Validações'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Planejado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Lista - Validações'!$A$12:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lista - Validações'!$B$12:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9C6-46DD-9321-4A07144E7EE7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lista - Validações'!$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Entregue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Lista - Validações'!$A$12:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lista - Validações'!$C$12:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C9C6-46DD-9321-4A07144E7EE7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1023516176"/>
+        <c:axId val="1023518096"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1023516176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1023518096"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1023518096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1023516176"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3634741</xdr:colOff>
+      <xdr:colOff>2606500</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>73078</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5539740</xdr:colOff>
+      <xdr:colOff>4511499</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1301250</xdr:rowOff>
+      <xdr:rowOff>1282888</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -535,7 +1587,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5349241" y="91440"/>
+          <a:off x="6618476" y="73078"/>
           <a:ext cx="1904999" cy="1209810"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -545,30 +1597,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>18361</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>128530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>36723</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>117513</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3209FD1-FFB7-48BF-9C12-730F6DFA304F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Backlog_AGGRAN"/>
-      <sheetName val="Lista - validações"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -888,17 +1955,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D93D68-5FF0-4B09-AF11-20EA4B06C9C2}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="104.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
@@ -906,14 +1973,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -940,619 +2007,695 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="20">
+        <v>5</v>
+      </c>
+      <c r="F3" s="20">
+        <v>1</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" s="10">
+        <f>SUM($E$1:$E$25)</f>
+        <v>145</v>
+      </c>
+      <c r="L3" s="10">
+        <f>SUM($E$1:$E$25)</f>
+        <v>145</v>
+      </c>
+      <c r="M3" s="10"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="16">
+        <v>5</v>
+      </c>
+      <c r="F4" s="16">
+        <v>2</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="10">
+        <f>SUMIF($G$3:$G$25,J4,$E$3:$E$25)</f>
+        <v>145</v>
+      </c>
+      <c r="L4" s="10">
+        <f>SUMIF(G3:G25,J4,E3:E25)</f>
+        <v>145</v>
+      </c>
+      <c r="M4" s="10">
+        <f>SUMIFS($E3:$E25,$H3:$H25,$M$2,$G3:$G25,J4)</f>
+        <v>101</v>
+      </c>
+      <c r="N4" s="11">
+        <f>L4-M4</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="16">
+        <v>5</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="10">
+        <f>SUMIF($G$3:$G$25,J5,$E$3:$E$25)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <f>SUMIF(G4:G26,J5,E4:E26)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <f>SUMIFS($E4:$E26,$H4:$H26,$M$2,$G4:$G26,J5)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="11">
+        <f>L5-M5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="16">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="10">
+        <f>SUMIF($G$3:$G$25,J6,$E$3:$E$25)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <f>SUMIF(G5:G27,J6,E5:E27)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <f>SUMIFS($E5:$E27,$H5:$H27,$M$2,$G5:$G27,J6)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="11">
+        <f>L6-M6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="16">
+        <v>3</v>
+      </c>
+      <c r="F7" s="16">
+        <v>2</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="K7" s="12">
+        <f>ROUND(AVERAGE($E$3:$E$38),2)</f>
+        <v>6.3</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="16">
+        <v>5</v>
+      </c>
+      <c r="F8" s="16">
+        <v>2</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="16">
+        <v>8</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="14" t="s">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="16">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16">
+        <v>3</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="4" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D11" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E11" s="16">
         <v>5</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F11" s="16">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G11" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="16">
-        <f>SUM($E$1:$E$23)</f>
-        <v>135</v>
-      </c>
-      <c r="L3" s="16">
-        <f>SUMIF([1]!Tabela2[SPRINT],J3,[1]!Tabela2[TAM('#)])</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="16"/>
-      <c r="N3" s="17"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="16">
+        <v>13</v>
+      </c>
+      <c r="F12" s="16">
+        <v>1</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="16">
+        <v>13</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="16">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16">
+        <v>2</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E15" s="16">
         <v>5</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F15" s="16">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G15" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H15" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="16">
+        <v>5</v>
+      </c>
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="16" t="s">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="16">
+        <v>5</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="16">
-        <f>SUMIF($G$3:$G$23,J4,$E$3:$E$23)</f>
-        <v>135</v>
-      </c>
-      <c r="L4" s="16">
-        <f>SUMIF(G3:G23,J4,E3:E23)</f>
-        <v>135</v>
-      </c>
-      <c r="M4" s="16">
-        <f>SUMIFS($E3:$E23,$H3:$H23,$M$2,$G3:$G23,J4)</f>
-        <v>23</v>
-      </c>
-      <c r="N4" s="17">
-        <f>L4-M4</f>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="H17" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E18" s="16">
         <v>5</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F18" s="16">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G18" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H18" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D19" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="16">
+        <v>5</v>
+      </c>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="16">
+        <v>8</v>
+      </c>
+      <c r="F20" s="16">
+        <v>1</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="16">
+        <v>21</v>
+      </c>
+      <c r="F21" s="16">
         <v>3</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="16">
+        <v>5</v>
+      </c>
+      <c r="F22" s="16">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G22" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H22" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="16">
+        <v>5</v>
+      </c>
+      <c r="F23" s="16">
+        <v>1</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="16">
+        <v>5</v>
+      </c>
+      <c r="F24" s="16">
+        <v>1</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4" t="s">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="26">
+        <v>5</v>
+      </c>
+      <c r="F25" s="26">
+        <v>1</v>
+      </c>
+      <c r="G25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" s="18">
-        <f>ROUND(AVERAGE($E$3:$E$36),2)</f>
-        <v>6.43</v>
-      </c>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4">
-        <v>5</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="4">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4">
-        <v>3</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4">
-        <v>5</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="4">
-        <v>13</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4">
-        <v>3</v>
-      </c>
-      <c r="F14" s="4">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="4">
-        <v>5</v>
-      </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="4">
-        <v>5</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="4">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="4">
-        <v>5</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="4">
-        <v>8</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="4">
-        <v>21</v>
-      </c>
-      <c r="F20" s="4">
-        <v>3</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="4">
-        <v>5</v>
-      </c>
-      <c r="F21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="4">
-        <v>5</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="4">
-        <v>5</v>
-      </c>
-      <c r="F23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="H25" s="27" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1561,6 +2704,14 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A3:H25">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$H3="PENDENTE"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$H3="ENTREGUE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
   <extLst>
@@ -1610,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8A1F20-5CB4-437C-A32E-7BDF1EF31B1F}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1622,131 +2773,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>3</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>5</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>13</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>21</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>71</v>
+      <c r="A11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="10">
         <f>Backlog!L4</f>
-        <v>135</v>
-      </c>
-      <c r="C12" s="20">
+        <v>145</v>
+      </c>
+      <c r="C12" s="10">
         <f>Backlog!M4</f>
-        <v>23</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="10">
+        <f>Backlog!L5</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="10">
+        <f>Backlog!M5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10">
+        <f>Backlog!L6</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="10">
+        <f>Backlog!M6</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
